--- a/final/audit_FINAL.xlsx
+++ b/final/audit_FINAL.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1500"/>
+  <dimension ref="A1:P1502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67593,12 +67593,12 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>הריון / לידה</t>
+          <t>חדש בפייסבוק</t>
         </is>
       </c>
       <c r="C1434" t="inlineStr">
         <is>
-          <t>parenting_site</t>
+          <t>facebook_group_admin</t>
         </is>
       </c>
       <c r="D1434" t="inlineStr">
@@ -67608,35 +67608,23 @@
       </c>
       <c r="E1434" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F1434" t="inlineStr">
         <is>
-          <t>https://www.yoledet.co.il/</t>
-        </is>
-      </c>
-      <c r="G1434" t="inlineStr">
-        <is>
-          <t>eran1201@eran.org.il</t>
-        </is>
-      </c>
-      <c r="H1434" t="inlineStr">
-        <is>
-          <t>PERSONAL_PROFESSIONAL</t>
-        </is>
-      </c>
+          <t>https://www.pc.co.il/news/66422/</t>
+        </is>
+      </c>
+      <c r="G1434" t="inlineStr"/>
+      <c r="H1434" t="inlineStr"/>
       <c r="I1434" t="n">
-        <v>95</v>
-      </c>
-      <c r="J1434" t="inlineStr">
-        <is>
-          <t>https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J1434" t="inlineStr"/>
       <c r="K1434" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>NO_VERIFIED_PUBLIC_EMAIL</t>
         </is>
       </c>
     </row>
@@ -67646,12 +67634,12 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>קורסי דולות וקורסי מדריכות הכנה ללידה</t>
+          <t>קבוצת הריון מרובה עוברים</t>
         </is>
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>childbirth_school</t>
+          <t>facebook_group_admin</t>
         </is>
       </c>
       <c r="D1435" t="inlineStr">
@@ -67661,35 +67649,23 @@
       </c>
       <c r="E1435" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F1435" t="inlineStr">
         <is>
-          <t>https://www.israelidoula.co.il/courses-1</t>
-        </is>
-      </c>
-      <c r="G1435" t="inlineStr">
-        <is>
-          <t>sivan@israelidoula.co.il</t>
-        </is>
-      </c>
-      <c r="H1435" t="inlineStr">
-        <is>
-          <t>PERSONAL_PROFESSIONAL</t>
-        </is>
-      </c>
+          <t>https://www.yoledet.co.il/whatsapp-multiple-pregnancy/</t>
+        </is>
+      </c>
+      <c r="G1435" t="inlineStr"/>
+      <c r="H1435" t="inlineStr"/>
       <c r="I1435" t="n">
-        <v>90</v>
-      </c>
-      <c r="J1435" t="inlineStr">
-        <is>
-          <t>https://www.israelidoula.co.il/courses-1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J1435" t="inlineStr"/>
       <c r="K1435" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>NO_VERIFIED_PUBLIC_EMAIL</t>
         </is>
       </c>
     </row>
@@ -67699,12 +67675,12 @@
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>אודות אתר הפוריות של ישראל</t>
+          <t>הריון / לידה</t>
         </is>
       </c>
       <c r="C1436" t="inlineStr">
         <is>
-          <t>community_manager</t>
+          <t>parenting_site</t>
         </is>
       </c>
       <c r="D1436" t="inlineStr">
@@ -67714,30 +67690,30 @@
       </c>
       <c r="E1436" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>org</t>
         </is>
       </c>
       <c r="F1436" t="inlineStr">
         <is>
-          <t>https://www.israelivf.co.il/אודות/</t>
+          <t>https://www.yoledet.co.il/</t>
         </is>
       </c>
       <c r="G1436" t="inlineStr">
         <is>
-          <t>info@israelivf.co.il</t>
+          <t>eran1201@eran.org.il</t>
         </is>
       </c>
       <c r="H1436" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="I1436" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J1436" t="inlineStr">
         <is>
-          <t>https://www.israelivf.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/</t>
+          <t>https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/</t>
         </is>
       </c>
       <c r="K1436" t="inlineStr">
@@ -67752,12 +67728,12 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>אימהות ואבות בהריון ולאחר לידה</t>
+          <t>קורסי דולות וקורסי מדריכות הכנה ללידה</t>
         </is>
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>community_manager</t>
+          <t>childbirth_school</t>
         </is>
       </c>
       <c r="D1437" t="inlineStr">
@@ -67767,22 +67743,22 @@
       </c>
       <c r="E1437" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>org</t>
         </is>
       </c>
       <c r="F1437" t="inlineStr">
         <is>
-          <t>https://www.eran.org.il/eran-for-the-community/parents/</t>
+          <t>https://www.israelidoula.co.il/courses-1</t>
         </is>
       </c>
       <c r="G1437" t="inlineStr">
         <is>
-          <t>eran1201@eran.org.il</t>
+          <t>sivan@israelidoula.co.il</t>
         </is>
       </c>
       <c r="H1437" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="I1437" t="n">
@@ -67790,7 +67766,7 @@
       </c>
       <c r="J1437" t="inlineStr">
         <is>
-          <t>https://www.eran.org.il/eran-for-the-community/parents/</t>
+          <t>https://www.israelidoula.co.il/courses-1</t>
         </is>
       </c>
       <c r="K1437" t="inlineStr">
@@ -67805,7 +67781,7 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>אתר הפוריות של ישראל</t>
+          <t>אודות אתר הפוריות של ישראל</t>
         </is>
       </c>
       <c r="C1438" t="inlineStr">
@@ -67825,7 +67801,7 @@
       </c>
       <c r="F1438" t="inlineStr">
         <is>
-          <t>https://www.israelivf.co.il/</t>
+          <t>https://www.israelivf.co.il/אודות/</t>
         </is>
       </c>
       <c r="G1438" t="inlineStr">
@@ -67843,7 +67819,7 @@
       </c>
       <c r="J1438" t="inlineStr">
         <is>
-          <t>https://www.israelivf.co.il/%D7%A8%D7%A9%D7%99%D7%9E%D7%AA-%D7%A8%D7%95%D7%A4%D7%90%D7%99-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%99%D7%9D/</t>
+          <t>https://www.israelivf.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/</t>
         </is>
       </c>
       <c r="K1438" t="inlineStr">
@@ -67858,7 +67834,7 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>מילה של מיילדת</t>
+          <t>אימהות ואבות בהריון ולאחר לידה</t>
         </is>
       </c>
       <c r="C1439" t="inlineStr">
@@ -67878,12 +67854,12 @@
       </c>
       <c r="F1439" t="inlineStr">
         <is>
-          <t>https://midwives.org.il/mila-shel-meyaledet/</t>
+          <t>https://www.eran.org.il/eran-for-the-community/parents/</t>
         </is>
       </c>
       <c r="G1439" t="inlineStr">
         <is>
-          <t>midwivesil@midwives.org.il</t>
+          <t>eran1201@eran.org.il</t>
         </is>
       </c>
       <c r="H1439" t="inlineStr">
@@ -67896,7 +67872,7 @@
       </c>
       <c r="J1439" t="inlineStr">
         <is>
-          <t>https://midwives.org.il/trauma-clinics/</t>
+          <t>https://www.eran.org.il/eran-for-the-community/parents/</t>
         </is>
       </c>
       <c r="K1439" t="inlineStr">
@@ -67911,7 +67887,7 @@
       </c>
       <c r="B1440" t="inlineStr">
         <is>
-          <t>פורטל תינוק ישראלי</t>
+          <t>אתר הפוריות של ישראל</t>
         </is>
       </c>
       <c r="C1440" t="inlineStr">
@@ -67931,12 +67907,12 @@
       </c>
       <c r="F1440" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/</t>
+          <t>https://www.israelivf.co.il/</t>
         </is>
       </c>
       <c r="G1440" t="inlineStr">
         <is>
-          <t>marketing@israelibaby.co.il</t>
+          <t>info@israelivf.co.il</t>
         </is>
       </c>
       <c r="H1440" t="inlineStr">
@@ -67949,7 +67925,7 @@
       </c>
       <c r="J1440" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/about</t>
+          <t>https://www.israelivf.co.il/%D7%A8%D7%A9%D7%99%D7%9E%D7%AA-%D7%A8%D7%95%D7%A4%D7%90%D7%99-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%99%D7%9D/</t>
         </is>
       </c>
       <c r="K1440" t="inlineStr">
@@ -67964,7 +67940,7 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>פוריות</t>
+          <t>מילה של מיילדת</t>
         </is>
       </c>
       <c r="C1441" t="inlineStr">
@@ -67984,12 +67960,12 @@
       </c>
       <c r="F1441" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/Main/PodcastDetails.aspx</t>
+          <t>https://midwives.org.il/mila-shel-meyaledet/</t>
         </is>
       </c>
       <c r="G1441" t="inlineStr">
         <is>
-          <t>info@israelivf.co.il</t>
+          <t>midwivesil@midwives.org.il</t>
         </is>
       </c>
       <c r="H1441" t="inlineStr">
@@ -68002,7 +67978,7 @@
       </c>
       <c r="J1441" t="inlineStr">
         <is>
-          <t>https://www.israelivf.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/</t>
+          <t>https://midwives.org.il/trauma-clinics/</t>
         </is>
       </c>
       <c r="K1441" t="inlineStr">
@@ -68017,12 +67993,12 @@
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>קורס דולות</t>
+          <t>פורטל תינוק ישראלי</t>
         </is>
       </c>
       <c r="C1442" t="inlineStr">
         <is>
-          <t>doula_school</t>
+          <t>community_manager</t>
         </is>
       </c>
       <c r="D1442" t="inlineStr">
@@ -68032,22 +68008,22 @@
       </c>
       <c r="E1442" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F1442" t="inlineStr">
         <is>
-          <t>http://www.leida-school.co.il/</t>
+          <t>https://www.israelibaby.co.il/</t>
         </is>
       </c>
       <c r="G1442" t="inlineStr">
         <is>
-          <t>office@be-doula.co.il</t>
+          <t>marketing@israelibaby.co.il</t>
         </is>
       </c>
       <c r="H1442" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>BUSINESS_OR_COMMUNITY</t>
         </is>
       </c>
       <c r="I1442" t="n">
@@ -68055,7 +68031,7 @@
       </c>
       <c r="J1442" t="inlineStr">
         <is>
-          <t>https://be-doula.co.il/%D7%A7%D7%95%D7%A8%D7%A1-%D7%93%D7%95%D7%9C%D7%95%D7%AA/</t>
+          <t>https://www.israelibaby.co.il/about</t>
         </is>
       </c>
       <c r="K1442" t="inlineStr">
@@ -68070,12 +68046,12 @@
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>קורס דולות במסגרת תואר ראשון בניהול מערכות בריאות</t>
+          <t>פוריות</t>
         </is>
       </c>
       <c r="C1443" t="inlineStr">
         <is>
-          <t>doula_school</t>
+          <t>community_manager</t>
         </is>
       </c>
       <c r="D1443" t="inlineStr">
@@ -68085,22 +68061,22 @@
       </c>
       <c r="E1443" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F1443" t="inlineStr">
         <is>
-          <t>https://www.mishpat.ac.il/קורס-דולות-ניהול-מערכות-בריאות/</t>
+          <t>https://www.ima.org.il/Main/PodcastDetails.aspx</t>
         </is>
       </c>
       <c r="G1443" t="inlineStr">
         <is>
-          <t>yorama@mishpat.ac.il</t>
+          <t>info@israelivf.co.il</t>
         </is>
       </c>
       <c r="H1443" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>BUSINESS_OR_COMMUNITY</t>
         </is>
       </c>
       <c r="I1443" t="n">
@@ -68108,7 +68084,7 @@
       </c>
       <c r="J1443" t="inlineStr">
         <is>
-          <t>https://www.mishpat.ac.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/</t>
+          <t>https://www.israelivf.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/</t>
         </is>
       </c>
       <c r="K1443" t="inlineStr">
@@ -68123,7 +68099,7 @@
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>קורסי דולות וקורסי מדריכות הכנה ללידה</t>
+          <t>קורס דולות</t>
         </is>
       </c>
       <c r="C1444" t="inlineStr">
@@ -68143,17 +68119,17 @@
       </c>
       <c r="F1444" t="inlineStr">
         <is>
-          <t>https://www.israelidoula.co.il/courses-1</t>
+          <t>http://www.leida-school.co.il/</t>
         </is>
       </c>
       <c r="G1444" t="inlineStr">
         <is>
-          <t>sivan@israelidoula.co.il</t>
+          <t>office@be-doula.co.il</t>
         </is>
       </c>
       <c r="H1444" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="I1444" t="n">
@@ -68161,7 +68137,7 @@
       </c>
       <c r="J1444" t="inlineStr">
         <is>
-          <t>https://www.israelidoula.co.il/courses-1</t>
+          <t>https://be-doula.co.il/%D7%A7%D7%95%D7%A8%D7%A1-%D7%93%D7%95%D7%9C%D7%95%D7%AA/</t>
         </is>
       </c>
       <c r="K1444" t="inlineStr">
@@ -68176,12 +68152,12 @@
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>אתר הפוריות של ישראל</t>
+          <t>קורס דולות במסגרת תואר ראשון בניהול מערכות בריאות</t>
         </is>
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>facebook_group_admin</t>
+          <t>doula_school</t>
         </is>
       </c>
       <c r="D1445" t="inlineStr">
@@ -68191,22 +68167,22 @@
       </c>
       <c r="E1445" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>org</t>
         </is>
       </c>
       <c r="F1445" t="inlineStr">
         <is>
-          <t>https://www.israelivf.co.il/</t>
+          <t>https://www.mishpat.ac.il/קורס-דולות-ניהול-מערכות-בריאות/</t>
         </is>
       </c>
       <c r="G1445" t="inlineStr">
         <is>
-          <t>info@israelivf.co.il</t>
+          <t>yorama@mishpat.ac.il</t>
         </is>
       </c>
       <c r="H1445" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="I1445" t="n">
@@ -68214,7 +68190,7 @@
       </c>
       <c r="J1445" t="inlineStr">
         <is>
-          <t>https://www.israelivf.co.il/%D7%A8%D7%A9%D7%99%D7%9E%D7%AA-%D7%A8%D7%95%D7%A4%D7%90%D7%99-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%99%D7%9D/</t>
+          <t>https://www.mishpat.ac.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8/</t>
         </is>
       </c>
       <c r="K1445" t="inlineStr">
@@ -68229,12 +68205,12 @@
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>טיפולי פוריות</t>
+          <t>קורסי דולות וקורסי מדריכות הכנה ללידה</t>
         </is>
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>facebook_group_admin</t>
+          <t>doula_school</t>
         </is>
       </c>
       <c r="D1446" t="inlineStr">
@@ -68244,22 +68220,22 @@
       </c>
       <c r="E1446" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>org</t>
         </is>
       </c>
       <c r="F1446" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/2097360377179819/</t>
+          <t>https://www.israelidoula.co.il/courses-1</t>
         </is>
       </c>
       <c r="G1446" t="inlineStr">
         <is>
-          <t>annette@annette.co.il</t>
+          <t>sivan@israelidoula.co.il</t>
         </is>
       </c>
       <c r="H1446" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="I1446" t="n">
@@ -68267,7 +68243,7 @@
       </c>
       <c r="J1446" t="inlineStr">
         <is>
-          <t>https://www.annette.co.il/about_heb/</t>
+          <t>https://www.israelidoula.co.il/courses-1</t>
         </is>
       </c>
       <c r="K1446" t="inlineStr">
@@ -68282,7 +68258,7 @@
       </c>
       <c r="B1447" t="inlineStr">
         <is>
-          <t>טיפולי פוריות בהתאמה אישית</t>
+          <t>אתר הפוריות של ישראל</t>
         </is>
       </c>
       <c r="C1447" t="inlineStr">
@@ -68302,12 +68278,12 @@
       </c>
       <c r="F1447" t="inlineStr">
         <is>
-          <t>https://www.greenfertility.co.il/</t>
+          <t>https://www.israelivf.co.il/</t>
         </is>
       </c>
       <c r="G1447" t="inlineStr">
         <is>
-          <t>ivf@greenfertility.co.il</t>
+          <t>info@israelivf.co.il</t>
         </is>
       </c>
       <c r="H1447" t="inlineStr">
@@ -68320,7 +68296,7 @@
       </c>
       <c r="J1447" t="inlineStr">
         <is>
-          <t>https://www.greenfertility.co.il/contact-dr-green/</t>
+          <t>https://www.israelivf.co.il/%D7%A8%D7%A9%D7%99%D7%9E%D7%AA-%D7%A8%D7%95%D7%A4%D7%90%D7%99-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%99%D7%9D/</t>
         </is>
       </c>
       <c r="K1447" t="inlineStr">
@@ -68335,7 +68311,7 @@
       </c>
       <c r="B1448" t="inlineStr">
         <is>
-          <t>קניה ומכירה של תרופות פריון</t>
+          <t>טיפולי פוריות</t>
         </is>
       </c>
       <c r="C1448" t="inlineStr">
@@ -68355,12 +68331,12 @@
       </c>
       <c r="F1448" t="inlineStr">
         <is>
-          <t>https://www.israelivf.co.il/קניה-ומכירה-של-תרופות-פריון/</t>
+          <t>https://www.facebook.com/groups/2097360377179819/</t>
         </is>
       </c>
       <c r="G1448" t="inlineStr">
         <is>
-          <t>info@israelivf.co.il</t>
+          <t>annette@annette.co.il</t>
         </is>
       </c>
       <c r="H1448" t="inlineStr">
@@ -68373,7 +68349,7 @@
       </c>
       <c r="J1448" t="inlineStr">
         <is>
-          <t>https://www.israelivf.co.il/%D7%A7%D7%A0%D7%99%D7%94-%D7%95%D7%9E%D7%9B%D7%99%D7%A8%D7%94-%D7%A9%D7%9C-%D7%AA%D7%A8%D7%95%D7%A4%D7%95%D7%AA-%D7%A4%D7%A8%D7%99%D7%95%D7%9F/</t>
+          <t>https://www.annette.co.il/about_heb/</t>
         </is>
       </c>
       <c r="K1448" t="inlineStr">
@@ -68388,7 +68364,7 @@
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>שלפוחית השתן שלנו</t>
+          <t>טיפולי פוריות בהתאמה אישית</t>
         </is>
       </c>
       <c r="C1449" t="inlineStr">
@@ -68408,12 +68384,12 @@
       </c>
       <c r="F1449" t="inlineStr">
         <is>
-          <t>https://midwives.org.il/שלפוחית-שתן/</t>
+          <t>https://www.greenfertility.co.il/</t>
         </is>
       </c>
       <c r="G1449" t="inlineStr">
         <is>
-          <t>midwivesil@midwives.org.il</t>
+          <t>ivf@greenfertility.co.il</t>
         </is>
       </c>
       <c r="H1449" t="inlineStr">
@@ -68426,7 +68402,7 @@
       </c>
       <c r="J1449" t="inlineStr">
         <is>
-          <t>https://midwives.org.il/%D7%A9%D7%9C%D7%A4%D7%95%D7%97%D7%99%D7%AA-%D7%A9%D7%AA%D7%9F/#contact</t>
+          <t>https://www.greenfertility.co.il/contact-dr-green/</t>
         </is>
       </c>
       <c r="K1449" t="inlineStr">
@@ -68441,7 +68417,7 @@
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>תינוק ישראלי Official</t>
+          <t>קניה ומכירה של תרופות פריון</t>
         </is>
       </c>
       <c r="C1450" t="inlineStr">
@@ -68461,12 +68437,12 @@
       </c>
       <c r="F1450" t="inlineStr">
         <is>
-          <t>https://linktr.ee/israelibaby</t>
+          <t>https://www.israelivf.co.il/קניה-ומכירה-של-תרופות-פריון/</t>
         </is>
       </c>
       <c r="G1450" t="inlineStr">
         <is>
-          <t>marketing@israelibaby.co.il</t>
+          <t>info@israelivf.co.il</t>
         </is>
       </c>
       <c r="H1450" t="inlineStr">
@@ -68479,7 +68455,7 @@
       </c>
       <c r="J1450" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/about</t>
+          <t>https://www.israelivf.co.il/%D7%A7%D7%A0%D7%99%D7%94-%D7%95%D7%9E%D7%9B%D7%99%D7%A8%D7%94-%D7%A9%D7%9C-%D7%AA%D7%A8%D7%95%D7%A4%D7%95%D7%AA-%D7%A4%D7%A8%D7%99%D7%95%D7%9F/</t>
         </is>
       </c>
       <c r="K1450" t="inlineStr">
@@ -68494,12 +68470,12 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>אתר הפוריות של ישראל</t>
+          <t>שלפוחית השתן שלנו</t>
         </is>
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>instagram_creator</t>
+          <t>facebook_group_admin</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr">
@@ -68509,17 +68485,17 @@
       </c>
       <c r="E1451" t="inlineStr">
         <is>
-          <t>creator</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F1451" t="inlineStr">
         <is>
-          <t>https://www.israelivf.co.il/</t>
+          <t>https://midwives.org.il/שלפוחית-שתן/</t>
         </is>
       </c>
       <c r="G1451" t="inlineStr">
         <is>
-          <t>info@israelivf.co.il</t>
+          <t>midwivesil@midwives.org.il</t>
         </is>
       </c>
       <c r="H1451" t="inlineStr">
@@ -68532,7 +68508,7 @@
       </c>
       <c r="J1451" t="inlineStr">
         <is>
-          <t>https://www.israelivf.co.il/%D7%A8%D7%A9%D7%99%D7%9E%D7%AA-%D7%A8%D7%95%D7%A4%D7%90%D7%99-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%99%D7%9D/</t>
+          <t>https://midwives.org.il/%D7%A9%D7%9C%D7%A4%D7%95%D7%97%D7%99%D7%AA-%D7%A9%D7%AA%D7%9F/#contact</t>
         </is>
       </c>
       <c r="K1451" t="inlineStr">
@@ -68547,12 +68523,12 @@
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>הריון / לידה</t>
+          <t>תינוק ישראלי Official</t>
         </is>
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>instagram_creator</t>
+          <t>facebook_group_admin</t>
         </is>
       </c>
       <c r="D1452" t="inlineStr">
@@ -68562,12 +68538,12 @@
       </c>
       <c r="E1452" t="inlineStr">
         <is>
-          <t>creator</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F1452" t="inlineStr">
         <is>
-          <t>https://www.yoledet.co.il/</t>
+          <t>https://linktr.ee/israelibaby</t>
         </is>
       </c>
       <c r="G1452" t="inlineStr">
@@ -68600,7 +68576,7 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>הריון ולידה</t>
+          <t>אתר הפוריות של ישראל</t>
         </is>
       </c>
       <c r="C1453" t="inlineStr">
@@ -68620,12 +68596,12 @@
       </c>
       <c r="F1453" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/israelibaby.group/</t>
+          <t>https://www.israelivf.co.il/</t>
         </is>
       </c>
       <c r="G1453" t="inlineStr">
         <is>
-          <t>michal@laledet-beahava.co.il</t>
+          <t>info@israelivf.co.il</t>
         </is>
       </c>
       <c r="H1453" t="inlineStr">
@@ -68638,7 +68614,7 @@
       </c>
       <c r="J1453" t="inlineStr">
         <is>
-          <t>https://laledet-beahava.co.il/%D7%99%D7%A6%D7%99%D7%A8%D7%AA-%D7%A7%D7%A9%D7%A8/</t>
+          <t>https://www.israelivf.co.il/%D7%A8%D7%A9%D7%99%D7%9E%D7%AA-%D7%A8%D7%95%D7%A4%D7%90%D7%99-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%9E%D7%95%D7%9E%D7%9C%D7%A6%D7%99%D7%9D/</t>
         </is>
       </c>
       <c r="K1453" t="inlineStr">
@@ -68653,7 +68629,7 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>טיפולי פוריות</t>
+          <t>הריון / לידה</t>
         </is>
       </c>
       <c r="C1454" t="inlineStr">
@@ -68673,12 +68649,12 @@
       </c>
       <c r="F1454" t="inlineStr">
         <is>
-          <t>https://www.kan.org.il/tags/generaltags/טיפולי-פוריות/</t>
+          <t>https://www.yoledet.co.il/</t>
         </is>
       </c>
       <c r="G1454" t="inlineStr">
         <is>
-          <t>ivf@greenfertility.co.il</t>
+          <t>marketing@israelibaby.co.il</t>
         </is>
       </c>
       <c r="H1454" t="inlineStr">
@@ -68691,7 +68667,7 @@
       </c>
       <c r="J1454" t="inlineStr">
         <is>
-          <t>https://www.greenfertility.co.il/contact-dr-green/</t>
+          <t>https://www.israelibaby.co.il/about</t>
         </is>
       </c>
       <c r="K1454" t="inlineStr">
@@ -68706,7 +68682,7 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>פורטל תינוק ישראלי</t>
+          <t>הריון ולידה</t>
         </is>
       </c>
       <c r="C1455" t="inlineStr">
@@ -68726,12 +68702,12 @@
       </c>
       <c r="F1455" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/</t>
+          <t>https://www.facebook.com/groups/israelibaby.group/</t>
         </is>
       </c>
       <c r="G1455" t="inlineStr">
         <is>
-          <t>marketing@israelibaby.co.il</t>
+          <t>michal@laledet-beahava.co.il</t>
         </is>
       </c>
       <c r="H1455" t="inlineStr">
@@ -68744,7 +68720,7 @@
       </c>
       <c r="J1455" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/about</t>
+          <t>https://laledet-beahava.co.il/%D7%99%D7%A6%D7%99%D7%A8%D7%AA-%D7%A7%D7%A9%D7%A8/</t>
         </is>
       </c>
       <c r="K1455" t="inlineStr">
@@ -68759,7 +68735,7 @@
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>תוכן ליולדות</t>
+          <t>טיפולי פוריות</t>
         </is>
       </c>
       <c r="C1456" t="inlineStr">
@@ -68779,12 +68755,12 @@
       </c>
       <c r="F1456" t="inlineStr">
         <is>
-          <t>https://midwives.org.il/motherspage/</t>
+          <t>https://www.kan.org.il/tags/generaltags/טיפולי-פוריות/</t>
         </is>
       </c>
       <c r="G1456" t="inlineStr">
         <is>
-          <t>midwivesil@midwives.org.il</t>
+          <t>ivf@greenfertility.co.il</t>
         </is>
       </c>
       <c r="H1456" t="inlineStr">
@@ -68797,7 +68773,7 @@
       </c>
       <c r="J1456" t="inlineStr">
         <is>
-          <t>https://midwives.org.il/motherspage/#contact</t>
+          <t>https://www.greenfertility.co.il/contact-dr-green/</t>
         </is>
       </c>
       <c r="K1456" t="inlineStr">
@@ -68812,7 +68788,7 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>תינוק ישראלי Official</t>
+          <t>פורטל תינוק ישראלי</t>
         </is>
       </c>
       <c r="C1457" t="inlineStr">
@@ -68832,7 +68808,7 @@
       </c>
       <c r="F1457" t="inlineStr">
         <is>
-          <t>https://linktr.ee/israelibaby</t>
+          <t>https://www.israelibaby.co.il/</t>
         </is>
       </c>
       <c r="G1457" t="inlineStr">
@@ -68865,12 +68841,12 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>פורטל תינוק ישראלי</t>
+          <t>תוכן ליולדות</t>
         </is>
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>parenting_site</t>
+          <t>instagram_creator</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr">
@@ -68880,22 +68856,22 @@
       </c>
       <c r="E1458" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>creator</t>
         </is>
       </c>
       <c r="F1458" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/</t>
+          <t>https://midwives.org.il/motherspage/</t>
         </is>
       </c>
       <c r="G1458" t="inlineStr">
         <is>
-          <t>marketing@israelibaby.co.il</t>
+          <t>midwivesil@midwives.org.il</t>
         </is>
       </c>
       <c r="H1458" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>BUSINESS_OR_COMMUNITY</t>
         </is>
       </c>
       <c r="I1458" t="n">
@@ -68903,7 +68879,7 @@
       </c>
       <c r="J1458" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/about</t>
+          <t>https://midwives.org.il/motherspage/#contact</t>
         </is>
       </c>
       <c r="K1458" t="inlineStr">
@@ -68918,12 +68894,12 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>פלטפורמת החיפוש של ארגון המיילדות בישראל</t>
+          <t>תינוק ישראלי Official</t>
         </is>
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>parenting_site</t>
+          <t>instagram_creator</t>
         </is>
       </c>
       <c r="D1459" t="inlineStr">
@@ -68933,22 +68909,22 @@
       </c>
       <c r="E1459" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>creator</t>
         </is>
       </c>
       <c r="F1459" t="inlineStr">
         <is>
-          <t>https://find.midwives.org.il/</t>
+          <t>https://linktr.ee/israelibaby</t>
         </is>
       </c>
       <c r="G1459" t="inlineStr">
         <is>
-          <t>info@midwives.org.il</t>
+          <t>marketing@israelibaby.co.il</t>
         </is>
       </c>
       <c r="H1459" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>BUSINESS_OR_COMMUNITY</t>
         </is>
       </c>
       <c r="I1459" t="n">
@@ -68956,7 +68932,7 @@
       </c>
       <c r="J1459" t="inlineStr">
         <is>
-          <t>https://find.midwives.org.il/</t>
+          <t>https://www.israelibaby.co.il/about</t>
         </is>
       </c>
       <c r="K1459" t="inlineStr">
@@ -68971,12 +68947,12 @@
       </c>
       <c r="B1460" t="inlineStr">
         <is>
-          <t>אודות המרכז לחקר וקידום בריאות האישה</t>
+          <t>פורטל תינוק ישראלי</t>
         </is>
       </c>
       <c r="C1460" t="inlineStr">
         <is>
-          <t>women_health_creator</t>
+          <t>parenting_site</t>
         </is>
       </c>
       <c r="D1460" t="inlineStr">
@@ -68986,22 +68962,22 @@
       </c>
       <c r="E1460" t="inlineStr">
         <is>
-          <t>creator</t>
+          <t>org</t>
         </is>
       </c>
       <c r="F1460" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/u/research-centers/womancenter/about/</t>
+          <t>https://www.israelibaby.co.il/</t>
         </is>
       </c>
       <c r="G1460" t="inlineStr">
         <is>
-          <t>womcen@bgu.ac.il</t>
+          <t>marketing@israelibaby.co.il</t>
         </is>
       </c>
       <c r="H1460" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="I1460" t="n">
@@ -69009,7 +68985,7 @@
       </c>
       <c r="J1460" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il:443/u/research-centers/womancenter/about/</t>
+          <t>https://www.israelibaby.co.il/about</t>
         </is>
       </c>
       <c r="K1460" t="inlineStr">
@@ -69024,12 +69000,12 @@
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>בלוג</t>
+          <t>פלטפורמת החיפוש של ארגון המיילדות בישראל</t>
         </is>
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>women_health_creator</t>
+          <t>parenting_site</t>
         </is>
       </c>
       <c r="D1461" t="inlineStr">
@@ -69039,22 +69015,22 @@
       </c>
       <c r="E1461" t="inlineStr">
         <is>
-          <t>creator</t>
+          <t>org</t>
         </is>
       </c>
       <c r="F1461" t="inlineStr">
         <is>
-          <t>https://bri.co.il/בלוג/</t>
+          <t>https://find.midwives.org.il/</t>
         </is>
       </c>
       <c r="G1461" t="inlineStr">
         <is>
-          <t>sec101@bri.co.il</t>
+          <t>info@midwives.org.il</t>
         </is>
       </c>
       <c r="H1461" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="I1461" t="n">
@@ -69062,7 +69038,7 @@
       </c>
       <c r="J1461" t="inlineStr">
         <is>
-          <t>https://bri.co.il/areas_of_activity/%D7%9E%D7%A8%D7%A4%D7%90%D7%94-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%AA-%D7%90%D7%A0%D7%93%D7%95%D7%A7%D7%A8%D7%99%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/</t>
+          <t>https://find.midwives.org.il/</t>
         </is>
       </c>
       <c r="K1461" t="inlineStr">
@@ -69077,7 +69053,7 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>הריון / לידה</t>
+          <t>אודות המרכז לחקר וקידום בריאות האישה</t>
         </is>
       </c>
       <c r="C1462" t="inlineStr">
@@ -69097,12 +69073,12 @@
       </c>
       <c r="F1462" t="inlineStr">
         <is>
-          <t>https://www.yoledet.co.il/</t>
+          <t>https://www.bgu.ac.il/u/research-centers/womancenter/about/</t>
         </is>
       </c>
       <c r="G1462" t="inlineStr">
         <is>
-          <t>marketing@israelibaby.co.il</t>
+          <t>womcen@bgu.ac.il</t>
         </is>
       </c>
       <c r="H1462" t="inlineStr">
@@ -69115,7 +69091,7 @@
       </c>
       <c r="J1462" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/about</t>
+          <t>https://www.bgu.ac.il:443/u/research-centers/womancenter/about/</t>
         </is>
       </c>
       <c r="K1462" t="inlineStr">
@@ -69130,7 +69106,7 @@
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>פורטל תינוק ישראלי</t>
+          <t>בלוג</t>
         </is>
       </c>
       <c r="C1463" t="inlineStr">
@@ -69150,12 +69126,12 @@
       </c>
       <c r="F1463" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/</t>
+          <t>https://bri.co.il/בלוג/</t>
         </is>
       </c>
       <c r="G1463" t="inlineStr">
         <is>
-          <t>marketing@israelibaby.co.il</t>
+          <t>sec101@bri.co.il</t>
         </is>
       </c>
       <c r="H1463" t="inlineStr">
@@ -69168,7 +69144,7 @@
       </c>
       <c r="J1463" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/about</t>
+          <t>https://bri.co.il/areas_of_activity/%D7%9E%D7%A8%D7%A4%D7%90%D7%94-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%AA-%D7%90%D7%A0%D7%93%D7%95%D7%A7%D7%A8%D7%99%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/</t>
         </is>
       </c>
       <c r="K1463" t="inlineStr">
@@ -69183,7 +69159,7 @@
       </c>
       <c r="B1464" t="inlineStr">
         <is>
-          <t>צוות</t>
+          <t>הריון / לידה</t>
         </is>
       </c>
       <c r="C1464" t="inlineStr">
@@ -69203,12 +69179,12 @@
       </c>
       <c r="F1464" t="inlineStr">
         <is>
-          <t>https://www.briah.org/team</t>
+          <t>https://www.yoledet.co.il/</t>
         </is>
       </c>
       <c r="G1464" t="inlineStr">
         <is>
-          <t>tal@briah.org</t>
+          <t>marketing@israelibaby.co.il</t>
         </is>
       </c>
       <c r="H1464" t="inlineStr">
@@ -69221,7 +69197,7 @@
       </c>
       <c r="J1464" t="inlineStr">
         <is>
-          <t>https://www.briah.org/contact</t>
+          <t>https://www.israelibaby.co.il/about</t>
         </is>
       </c>
       <c r="K1464" t="inlineStr">
@@ -69236,7 +69212,7 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>צוות המרכז לחקר וקידום בריאות האישה</t>
+          <t>פורטל תינוק ישראלי</t>
         </is>
       </c>
       <c r="C1465" t="inlineStr">
@@ -69256,12 +69232,12 @@
       </c>
       <c r="F1465" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/u/research-centers/womancenter/staffmembers/</t>
+          <t>https://www.israelibaby.co.il/</t>
         </is>
       </c>
       <c r="G1465" t="inlineStr">
         <is>
-          <t>womcen@bgu.ac.il</t>
+          <t>marketing@israelibaby.co.il</t>
         </is>
       </c>
       <c r="H1465" t="inlineStr">
@@ -69274,7 +69250,7 @@
       </c>
       <c r="J1465" t="inlineStr">
         <is>
-          <t>https://www.bgu.ac.il/u/research-centers/womancenter/about/</t>
+          <t>https://www.israelibaby.co.il/about</t>
         </is>
       </c>
       <c r="K1465" t="inlineStr">
@@ -69289,12 +69265,12 @@
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>פוריות ופריון</t>
+          <t>צוות</t>
         </is>
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>community_manager</t>
+          <t>women_health_creator</t>
         </is>
       </c>
       <c r="D1466" t="inlineStr">
@@ -69304,17 +69280,17 @@
       </c>
       <c r="E1466" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>creator</t>
         </is>
       </c>
       <c r="F1466" t="inlineStr">
         <is>
-          <t>https://www.leumit.co.il/fertility/</t>
+          <t>https://www.briah.org/team</t>
         </is>
       </c>
       <c r="G1466" t="inlineStr">
         <is>
-          <t>clinic@hourvitz.co.il</t>
+          <t>tal@briah.org</t>
         </is>
       </c>
       <c r="H1466" t="inlineStr">
@@ -69327,7 +69303,7 @@
       </c>
       <c r="J1466" t="inlineStr">
         <is>
-          <t>https://www.hourvitz.co.il/contact/</t>
+          <t>https://www.briah.org/contact</t>
         </is>
       </c>
       <c r="K1466" t="inlineStr">
@@ -69342,12 +69318,12 @@
       </c>
       <c r="B1467" t="inlineStr">
         <is>
-          <t>את מי תזמיני להצטרף אליך אל חוויית הלידה?</t>
+          <t>צוות המרכז לחקר וקידום בריאות האישה</t>
         </is>
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>facebook_group_admin</t>
+          <t>women_health_creator</t>
         </is>
       </c>
       <c r="D1467" t="inlineStr">
@@ -69357,17 +69333,17 @@
       </c>
       <c r="E1467" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>creator</t>
         </is>
       </c>
       <c r="F1467" t="inlineStr">
         <is>
-          <t>https://midwives.org.il/את-מי-תזמיני-להצטרף-אליך-אל-חוויית-הליד/</t>
+          <t>https://www.bgu.ac.il/u/research-centers/womancenter/staffmembers/</t>
         </is>
       </c>
       <c r="G1467" t="inlineStr">
         <is>
-          <t>midwivesil@midwives.org.il</t>
+          <t>womcen@bgu.ac.il</t>
         </is>
       </c>
       <c r="H1467" t="inlineStr">
@@ -69380,7 +69356,7 @@
       </c>
       <c r="J1467" t="inlineStr">
         <is>
-          <t>https://midwives.org.il/%D7%90%D7%AA-%D7%9E%D7%99-%D7%AA%D7%96%D7%9E%D7%99%D7%A0%D7%99-%D7%9C%D7%94%D7%A6%D7%98%D7%A8%D7%A3-%D7%90%D7%9C%D7%99%D7%9A-%D7%90%D7%9C-%D7%97%D7%95%D7%95%D7%99%D7%99%D7%AA-%D7%94%D7%9C%D7%99%D7%93/#contact</t>
+          <t>https://www.bgu.ac.il/u/research-centers/womancenter/about/</t>
         </is>
       </c>
       <c r="K1467" t="inlineStr">
@@ -69395,12 +69371,12 @@
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>אגודה הישראלית לחקר הפוריות איל"ה</t>
+          <t>פוריות ופריון</t>
         </is>
       </c>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>instagram_creator</t>
+          <t>community_manager</t>
         </is>
       </c>
       <c r="D1468" t="inlineStr">
@@ -69410,17 +69386,17 @@
       </c>
       <c r="E1468" t="inlineStr">
         <is>
-          <t>creator</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F1468" t="inlineStr">
         <is>
-          <t>https://www.ayala.org.il/</t>
+          <t>https://www.leumit.co.il/fertility/</t>
         </is>
       </c>
       <c r="G1468" t="inlineStr">
         <is>
-          <t>knasim@ima.org.il</t>
+          <t>clinic@hourvitz.co.il</t>
         </is>
       </c>
       <c r="H1468" t="inlineStr">
@@ -69433,7 +69409,7 @@
       </c>
       <c r="J1468" t="inlineStr">
         <is>
-          <t>https://forms.ima.org.il/form/ifa2026</t>
+          <t>https://www.hourvitz.co.il/contact/</t>
         </is>
       </c>
       <c r="K1468" t="inlineStr">
@@ -69448,12 +69424,12 @@
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>פוריות</t>
+          <t>את מי תזמיני להצטרף אליך אל חוויית הלידה?</t>
         </is>
       </c>
       <c r="C1469" t="inlineStr">
         <is>
-          <t>instagram_creator</t>
+          <t>facebook_group_admin</t>
         </is>
       </c>
       <c r="D1469" t="inlineStr">
@@ -69463,17 +69439,17 @@
       </c>
       <c r="E1469" t="inlineStr">
         <is>
-          <t>creator</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F1469" t="inlineStr">
         <is>
-          <t>https://www1.health.gov.il/nursing/study/training-courses/training-list/fertility/</t>
+          <t>https://midwives.org.il/את-מי-תזמיני-להצטרף-אליך-אל-חוויית-הליד/</t>
         </is>
       </c>
       <c r="G1469" t="inlineStr">
         <is>
-          <t>call.habriut@moh.health.gov.il</t>
+          <t>midwivesil@midwives.org.il</t>
         </is>
       </c>
       <c r="H1469" t="inlineStr">
@@ -69486,7 +69462,7 @@
       </c>
       <c r="J1469" t="inlineStr">
         <is>
-          <t>https://www1.health.gov.il/nursing/study/training-courses/training-list/fertility/</t>
+          <t>https://midwives.org.il/%D7%90%D7%AA-%D7%9E%D7%99-%D7%AA%D7%96%D7%9E%D7%99%D7%A0%D7%99-%D7%9C%D7%94%D7%A6%D7%98%D7%A8%D7%A3-%D7%90%D7%9C%D7%99%D7%9A-%D7%90%D7%9C-%D7%97%D7%95%D7%95%D7%99%D7%99%D7%AA-%D7%94%D7%9C%D7%99%D7%93/#contact</t>
         </is>
       </c>
       <c r="K1469" t="inlineStr">
@@ -69501,12 +69477,12 @@
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>הריון</t>
+          <t>אגודה הישראלית לחקר הפוריות איל"ה</t>
         </is>
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>parenting_site</t>
+          <t>instagram_creator</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr">
@@ -69516,22 +69492,22 @@
       </c>
       <c r="E1470" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>creator</t>
         </is>
       </c>
       <c r="F1470" t="inlineStr">
         <is>
-          <t>https://www.yoledet.co.il/pregnancy/</t>
+          <t>https://www.ayala.org.il/</t>
         </is>
       </c>
       <c r="G1470" t="inlineStr">
         <is>
-          <t>marketing@israelibaby.co.il</t>
+          <t>knasim@ima.org.il</t>
         </is>
       </c>
       <c r="H1470" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>BUSINESS_OR_COMMUNITY</t>
         </is>
       </c>
       <c r="I1470" t="n">
@@ -69539,7 +69515,7 @@
       </c>
       <c r="J1470" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/about</t>
+          <t>https://forms.ima.org.il/form/ifa2026</t>
         </is>
       </c>
       <c r="K1470" t="inlineStr">
@@ -69554,12 +69530,12 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>מחשבון תאריך לידה משוער</t>
+          <t>פוריות</t>
         </is>
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>parenting_site</t>
+          <t>instagram_creator</t>
         </is>
       </c>
       <c r="D1471" t="inlineStr">
@@ -69569,22 +69545,22 @@
       </c>
       <c r="E1471" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>creator</t>
         </is>
       </c>
       <c r="F1471" t="inlineStr">
         <is>
-          <t>https://midwives.org.il/edd-calculation/</t>
+          <t>https://www1.health.gov.il/nursing/study/training-courses/training-list/fertility/</t>
         </is>
       </c>
       <c r="G1471" t="inlineStr">
         <is>
-          <t>midwivesil@midwives.org.il</t>
+          <t>call.habriut@moh.health.gov.il</t>
         </is>
       </c>
       <c r="H1471" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>BUSINESS_OR_COMMUNITY</t>
         </is>
       </c>
       <c r="I1471" t="n">
@@ -69592,7 +69568,7 @@
       </c>
       <c r="J1471" t="inlineStr">
         <is>
-          <t>https://midwives.org.il/trauma-clinics/</t>
+          <t>https://www1.health.gov.il/nursing/study/training-courses/training-list/fertility/</t>
         </is>
       </c>
       <c r="K1471" t="inlineStr">
@@ -69607,12 +69583,12 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>מעקב הריון</t>
+          <t>הריון</t>
         </is>
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>women_health_creator</t>
+          <t>parenting_site</t>
         </is>
       </c>
       <c r="D1472" t="inlineStr">
@@ -69622,22 +69598,22 @@
       </c>
       <c r="E1472" t="inlineStr">
         <is>
-          <t>creator</t>
+          <t>org</t>
         </is>
       </c>
       <c r="F1472" t="inlineStr">
         <is>
-          <t>https://www.midaat.org.il/articles/health-and-sickness/pregnancy-follow-up/</t>
+          <t>https://www.yoledet.co.il/pregnancy/</t>
         </is>
       </c>
       <c r="G1472" t="inlineStr">
         <is>
-          <t>sec101@bri.co.il</t>
+          <t>marketing@israelibaby.co.il</t>
         </is>
       </c>
       <c r="H1472" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="I1472" t="n">
@@ -69645,7 +69621,7 @@
       </c>
       <c r="J1472" t="inlineStr">
         <is>
-          <t>https://bri.co.il/areas_of_activity/%D7%9E%D7%A8%D7%A4%D7%90%D7%94-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%AA-%D7%90%D7%A0%D7%93%D7%95%D7%A7%D7%A8%D7%99%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/</t>
+          <t>https://www.israelibaby.co.il/about</t>
         </is>
       </c>
       <c r="K1472" t="inlineStr">
@@ -69660,12 +69636,12 @@
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>שבוע 37 להריון</t>
+          <t>מחשבון תאריך לידה משוער</t>
         </is>
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>instagram_creator</t>
+          <t>parenting_site</t>
         </is>
       </c>
       <c r="D1473" t="inlineStr">
@@ -69675,22 +69651,22 @@
       </c>
       <c r="E1473" t="inlineStr">
         <is>
-          <t>creator</t>
+          <t>org</t>
         </is>
       </c>
       <c r="F1473" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/שבוע-37-להריון</t>
+          <t>https://midwives.org.il/edd-calculation/</t>
         </is>
       </c>
       <c r="G1473" t="inlineStr">
         <is>
-          <t>marketing@israelibaby.co.il</t>
+          <t>midwivesil@midwives.org.il</t>
         </is>
       </c>
       <c r="H1473" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="I1473" t="n">
@@ -69698,7 +69674,7 @@
       </c>
       <c r="J1473" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/about</t>
+          <t>https://midwives.org.il/trauma-clinics/</t>
         </is>
       </c>
       <c r="K1473" t="inlineStr">
@@ -69713,12 +69689,12 @@
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>הריון ולידה</t>
+          <t>מעקב הריון</t>
         </is>
       </c>
       <c r="C1474" t="inlineStr">
         <is>
-          <t>pregnancy_podcast</t>
+          <t>women_health_creator</t>
         </is>
       </c>
       <c r="D1474" t="inlineStr">
@@ -69733,12 +69709,12 @@
       </c>
       <c r="F1474" t="inlineStr">
         <is>
-          <t>https://www.openu.ac.il/dean-students/adjustments_studies/pages/pregnancy_and_birth.aspx</t>
+          <t>https://www.midaat.org.il/articles/health-and-sickness/pregnancy-follow-up/</t>
         </is>
       </c>
       <c r="G1474" t="inlineStr">
         <is>
-          <t>yonief@openu.ac.il</t>
+          <t>sec101@bri.co.il</t>
         </is>
       </c>
       <c r="H1474" t="inlineStr">
@@ -69751,7 +69727,7 @@
       </c>
       <c r="J1474" t="inlineStr">
         <is>
-          <t>https://academic.openu.ac.il/history/pages/staff.aspx</t>
+          <t>https://bri.co.il/areas_of_activity/%D7%9E%D7%A8%D7%A4%D7%90%D7%94-%D7%9E%D7%98%D7%91%D7%95%D7%9C%D7%99%D7%AA-%D7%90%D7%A0%D7%93%D7%95%D7%A7%D7%A8%D7%99%D7%A0%D7%95%D7%9C%D7%95%D7%92%D7%99%D7%94/</t>
         </is>
       </c>
       <c r="K1474" t="inlineStr">
@@ -69766,12 +69742,12 @@
       </c>
       <c r="B1475" t="inlineStr">
         <is>
-          <t>פוריות ,הריון, לידה, הנקה משפחה וטרשת נפוצה</t>
+          <t>שבוע 37 להריון</t>
         </is>
       </c>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>pregnancy_podcast</t>
+          <t>instagram_creator</t>
         </is>
       </c>
       <c r="D1475" t="inlineStr">
@@ -69786,12 +69762,12 @@
       </c>
       <c r="F1475" t="inlineStr">
         <is>
-          <t>https://mssociety.org.il/category/אודות-טרשת-נפוצה/פוריות-הריון-לידה-והנקה/</t>
+          <t>https://www.israelibaby.co.il/שבוע-37-להריון</t>
         </is>
       </c>
       <c r="G1475" t="inlineStr">
         <is>
-          <t>agudaims@mssociety.org.il</t>
+          <t>marketing@israelibaby.co.il</t>
         </is>
       </c>
       <c r="H1475" t="inlineStr">
@@ -69804,7 +69780,7 @@
       </c>
       <c r="J1475" t="inlineStr">
         <is>
-          <t>https://mssociety.org.il/category/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%98%D7%A8%D7%A9%D7%AA-%D7%A0%D7%A4%D7%95%D7%A6%D7%94/%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A8%D7%99%D7%95%D7%9F-%D7%9C%D7%99%D7%93%D7%94-%D7%95%D7%94%D7%A0%D7%A7%D7%94/</t>
+          <t>https://www.israelibaby.co.il/about</t>
         </is>
       </c>
       <c r="K1475" t="inlineStr">
@@ -69819,12 +69795,12 @@
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>ליווי הריון ע"י מיילדת בקופת החולים שלך</t>
+          <t>הריון ולידה</t>
         </is>
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>community_manager</t>
+          <t>pregnancy_podcast</t>
         </is>
       </c>
       <c r="D1476" t="inlineStr">
@@ -69834,17 +69810,17 @@
       </c>
       <c r="E1476" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>creator</t>
         </is>
       </c>
       <c r="F1476" t="inlineStr">
         <is>
-          <t>https://midwives.org.il/midwife-pregnancy-folowup-clinics/</t>
+          <t>https://www.openu.ac.il/dean-students/adjustments_studies/pages/pregnancy_and_birth.aspx</t>
         </is>
       </c>
       <c r="G1476" t="inlineStr">
         <is>
-          <t>midwivesil@midwives.org.il</t>
+          <t>yonief@openu.ac.il</t>
         </is>
       </c>
       <c r="H1476" t="inlineStr">
@@ -69857,7 +69833,7 @@
       </c>
       <c r="J1476" t="inlineStr">
         <is>
-          <t>https://midwives.org.il/trauma-clinics/</t>
+          <t>https://academic.openu.ac.il/history/pages/staff.aspx</t>
         </is>
       </c>
       <c r="K1476" t="inlineStr">
@@ -69872,12 +69848,12 @@
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>הריון ולידה עם מיוטוניק דיסטרופי</t>
+          <t>פוריות ,הריון, לידה, הנקה משפחה וטרשת נפוצה</t>
         </is>
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>community_manager</t>
+          <t>pregnancy_podcast</t>
         </is>
       </c>
       <c r="D1477" t="inlineStr">
@@ -69887,17 +69863,17 @@
       </c>
       <c r="E1477" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>creator</t>
         </is>
       </c>
       <c r="F1477" t="inlineStr">
         <is>
-          <t>https://myotonic.co.il/pregnancy</t>
+          <t>https://mssociety.org.il/category/אודות-טרשת-נפוצה/פוריות-הריון-לידה-והנקה/</t>
         </is>
       </c>
       <c r="G1477" t="inlineStr">
         <is>
-          <t>community@myotonic.co.il</t>
+          <t>agudaims@mssociety.org.il</t>
         </is>
       </c>
       <c r="H1477" t="inlineStr">
@@ -69906,11 +69882,11 @@
         </is>
       </c>
       <c r="I1477" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J1477" t="inlineStr">
         <is>
-          <t>https://myotonic.co.il/about</t>
+          <t>https://mssociety.org.il/category/%D7%90%D7%95%D7%93%D7%95%D7%AA-%D7%98%D7%A8%D7%A9%D7%AA-%D7%A0%D7%A4%D7%95%D7%A6%D7%94/%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A8%D7%99%D7%95%D7%9F-%D7%9C%D7%99%D7%93%D7%94-%D7%95%D7%94%D7%A0%D7%A7%D7%94/</t>
         </is>
       </c>
       <c r="K1477" t="inlineStr">
@@ -69925,12 +69901,12 @@
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>בית הספר אמנות הלידה קורס דולות</t>
+          <t>ליווי הריון ע"י מיילדת בקופת החולים שלך</t>
         </is>
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>doula_school</t>
+          <t>community_manager</t>
         </is>
       </c>
       <c r="D1478" t="inlineStr">
@@ -69940,30 +69916,30 @@
       </c>
       <c r="E1478" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F1478" t="inlineStr">
         <is>
-          <t>https://www.leidaschool.co.il/</t>
+          <t>https://midwives.org.il/midwife-pregnancy-folowup-clinics/</t>
         </is>
       </c>
       <c r="G1478" t="inlineStr">
         <is>
-          <t>info@michlalot.co.il</t>
+          <t>midwivesil@midwives.org.il</t>
         </is>
       </c>
       <c r="H1478" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>BUSINESS_OR_COMMUNITY</t>
         </is>
       </c>
       <c r="I1478" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J1478" t="inlineStr">
         <is>
-          <t>https://www.michlalot.co.il/leida/main</t>
+          <t>https://midwives.org.il/trauma-clinics/</t>
         </is>
       </c>
       <c r="K1478" t="inlineStr">
@@ -69978,12 +69954,12 @@
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>דולה ישראלית</t>
+          <t>הריון ולידה עם מיוטוניק דיסטרופי</t>
         </is>
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>doula_school</t>
+          <t>community_manager</t>
         </is>
       </c>
       <c r="D1479" t="inlineStr">
@@ -69993,22 +69969,22 @@
       </c>
       <c r="E1479" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F1479" t="inlineStr">
         <is>
-          <t>https://www.israelidoula.co.il/courses-1</t>
+          <t>https://myotonic.co.il/pregnancy</t>
         </is>
       </c>
       <c r="G1479" t="inlineStr">
         <is>
-          <t>sivan@israelidoula.co.il</t>
+          <t>community@myotonic.co.il</t>
         </is>
       </c>
       <c r="H1479" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>BUSINESS_OR_COMMUNITY</t>
         </is>
       </c>
       <c r="I1479" t="n">
@@ -70016,7 +69992,7 @@
       </c>
       <c r="J1479" t="inlineStr">
         <is>
-          <t>https://www.israelidoula.co.il/courses-1</t>
+          <t>https://myotonic.co.il/about</t>
         </is>
       </c>
       <c r="K1479" t="inlineStr">
@@ -70031,12 +70007,12 @@
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>הריון ולידה</t>
+          <t>בית הספר אמנות הלידה קורס דולות</t>
         </is>
       </c>
       <c r="C1480" t="inlineStr">
         <is>
-          <t>facebook_group_admin</t>
+          <t>doula_school</t>
         </is>
       </c>
       <c r="D1480" t="inlineStr">
@@ -70046,22 +70022,22 @@
       </c>
       <c r="E1480" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>org</t>
         </is>
       </c>
       <c r="F1480" t="inlineStr">
         <is>
-          <t>https://www.ipts.org.il/</t>
+          <t>https://www.leidaschool.co.il/</t>
         </is>
       </c>
       <c r="G1480" t="inlineStr">
         <is>
-          <t>marketing@israelibaby.co.il</t>
+          <t>info@michlalot.co.il</t>
         </is>
       </c>
       <c r="H1480" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="I1480" t="n">
@@ -70069,7 +70045,7 @@
       </c>
       <c r="J1480" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/about</t>
+          <t>https://www.michlalot.co.il/leida/main</t>
         </is>
       </c>
       <c r="K1480" t="inlineStr">
@@ -70084,12 +70060,12 @@
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>הריון ולידה</t>
+          <t>דולה ישראלית</t>
         </is>
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>women_health_creator</t>
+          <t>doula_school</t>
         </is>
       </c>
       <c r="D1481" t="inlineStr">
@@ -70099,22 +70075,22 @@
       </c>
       <c r="E1481" t="inlineStr">
         <is>
-          <t>creator</t>
+          <t>org</t>
         </is>
       </c>
       <c r="F1481" t="inlineStr">
         <is>
-          <t>https://healthy.walla.co.il/category/590</t>
+          <t>https://www.israelidoula.co.il/courses-1</t>
         </is>
       </c>
       <c r="G1481" t="inlineStr">
         <is>
-          <t>marketing@israelibaby.co.il</t>
+          <t>sivan@israelidoula.co.il</t>
         </is>
       </c>
       <c r="H1481" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="I1481" t="n">
@@ -70122,7 +70098,7 @@
       </c>
       <c r="J1481" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/about</t>
+          <t>https://www.israelidoula.co.il/courses-1</t>
         </is>
       </c>
       <c r="K1481" t="inlineStr">
@@ -70137,12 +70113,12 @@
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>סיפורים אישיים</t>
+          <t>הריון ולידה</t>
         </is>
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>women_health_creator</t>
+          <t>facebook_group_admin</t>
         </is>
       </c>
       <c r="D1482" t="inlineStr">
@@ -70152,17 +70128,17 @@
       </c>
       <c r="E1482" t="inlineStr">
         <is>
-          <t>creator</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F1482" t="inlineStr">
         <is>
-          <t>https://www.cmv.co.il/blog/</t>
+          <t>https://www.ipts.org.il/</t>
         </is>
       </c>
       <c r="G1482" t="inlineStr">
         <is>
-          <t>office@boneiolam.co.il</t>
+          <t>marketing@israelibaby.co.il</t>
         </is>
       </c>
       <c r="H1482" t="inlineStr">
@@ -70175,7 +70151,7 @@
       </c>
       <c r="J1482" t="inlineStr">
         <is>
-          <t>https://boneiolam.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/</t>
+          <t>https://www.israelibaby.co.il/about</t>
         </is>
       </c>
       <c r="K1482" t="inlineStr">
@@ -70190,12 +70166,12 @@
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>סדנה לבעלים שנשותיהם עובדות טיפולי פוריות</t>
+          <t>הריון ולידה</t>
         </is>
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>facebook_group_admin</t>
+          <t>women_health_creator</t>
         </is>
       </c>
       <c r="D1483" t="inlineStr">
@@ -70205,17 +70181,17 @@
       </c>
       <c r="E1483" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>creator</t>
         </is>
       </c>
       <c r="F1483" t="inlineStr">
         <is>
-          <t>https://hospitals.clalit.co.il/carmel/he/news-articles/news-2025/Pages/workshop-for-husbands-whose-wives-are-undergoing-fertility-treatments.aspx</t>
+          <t>https://healthy.walla.co.il/category/590</t>
         </is>
       </c>
       <c r="G1483" t="inlineStr">
         <is>
-          <t>editor@karmel.co.il</t>
+          <t>marketing@israelibaby.co.il</t>
         </is>
       </c>
       <c r="H1483" t="inlineStr">
@@ -70228,7 +70204,7 @@
       </c>
       <c r="J1483" t="inlineStr">
         <is>
-          <t>https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%A1%D7%93%D7%A0%D7%94-%D7%9C%D7%91%D7%A2%D7%9C%D7%99%D7%9D-%D7%A9%D7%A0%D7%A9%D7%95%D7%AA%D7%99%D7%94%D7%9D-%D7%A2%D7%95%D7%91%D7%93%D7%95%D7%AA-%D7%98%D7%99%D7%A4%D7%95%D7%9C%D7%99-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA</t>
+          <t>https://www.israelibaby.co.il/about</t>
         </is>
       </c>
       <c r="K1483" t="inlineStr">
@@ -70243,12 +70219,12 @@
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>מחשבון הריון</t>
+          <t>סיפורים אישיים</t>
         </is>
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>parenting_site</t>
+          <t>women_health_creator</t>
         </is>
       </c>
       <c r="D1484" t="inlineStr">
@@ -70258,22 +70234,22 @@
       </c>
       <c r="E1484" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>creator</t>
         </is>
       </c>
       <c r="F1484" t="inlineStr">
         <is>
-          <t>https://www.yoledet.co.il/calculator/</t>
+          <t>https://www.cmv.co.il/blog/</t>
         </is>
       </c>
       <c r="G1484" t="inlineStr">
         <is>
-          <t>marketing@israelibaby.co.il</t>
+          <t>office@boneiolam.co.il</t>
         </is>
       </c>
       <c r="H1484" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>BUSINESS_OR_COMMUNITY</t>
         </is>
       </c>
       <c r="I1484" t="n">
@@ -70281,7 +70257,7 @@
       </c>
       <c r="J1484" t="inlineStr">
         <is>
-          <t>https://www.israelibaby.co.il/about</t>
+          <t>https://boneiolam.co.il/%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/</t>
         </is>
       </c>
       <c r="K1484" t="inlineStr">
@@ -70296,12 +70272,12 @@
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>קורסים לנשות מקצוע בתחום ההריון לידה והורות ראשונית</t>
+          <t>סדנה לבעלים שנשותיהם עובדות טיפולי פוריות</t>
         </is>
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>community_manager</t>
+          <t>facebook_group_admin</t>
         </is>
       </c>
       <c r="D1485" t="inlineStr">
@@ -70316,12 +70292,12 @@
       </c>
       <c r="F1485" t="inlineStr">
         <is>
-          <t>https://www.israelidoula.co.il/all-courses</t>
+          <t>https://hospitals.clalit.co.il/carmel/he/news-articles/news-2025/Pages/workshop-for-husbands-whose-wives-are-undergoing-fertility-treatments.aspx</t>
         </is>
       </c>
       <c r="G1485" t="inlineStr">
         <is>
-          <t>sivan@israelidoula.co.il</t>
+          <t>editor@karmel.co.il</t>
         </is>
       </c>
       <c r="H1485" t="inlineStr">
@@ -70334,7 +70310,7 @@
       </c>
       <c r="J1485" t="inlineStr">
         <is>
-          <t>https://www.israelidoula.co.il/all-courses</t>
+          <t>https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%A1%D7%93%D7%A0%D7%94-%D7%9C%D7%91%D7%A2%D7%9C%D7%99%D7%9D-%D7%A9%D7%A0%D7%A9%D7%95%D7%AA%D7%99%D7%94%D7%9D-%D7%A2%D7%95%D7%91%D7%93%D7%95%D7%AA-%D7%98%D7%99%D7%A4%D7%95%D7%9C%D7%99-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA</t>
         </is>
       </c>
       <c r="K1485" t="inlineStr">
@@ -70349,12 +70325,12 @@
       </c>
       <c r="B1486" t="inlineStr">
         <is>
-          <t>מעקב הריון שבועי</t>
+          <t>מחשבון הריון</t>
         </is>
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>women_health_creator</t>
+          <t>parenting_site</t>
         </is>
       </c>
       <c r="D1486" t="inlineStr">
@@ -70364,22 +70340,22 @@
       </c>
       <c r="E1486" t="inlineStr">
         <is>
-          <t>creator</t>
+          <t>org</t>
         </is>
       </c>
       <c r="F1486" t="inlineStr">
         <is>
-          <t>https://www.babylis.co.il/weekly-pregnancy-tracking-guide/</t>
+          <t>https://www.yoledet.co.il/calculator/</t>
         </is>
       </c>
       <c r="G1486" t="inlineStr">
         <is>
-          <t>info@medcalc.co.il</t>
+          <t>marketing@israelibaby.co.il</t>
         </is>
       </c>
       <c r="H1486" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="I1486" t="n">
@@ -70387,7 +70363,7 @@
       </c>
       <c r="J1486" t="inlineStr">
         <is>
-          <t>https://medcalc.co.il/contact/</t>
+          <t>https://www.israelibaby.co.il/about</t>
         </is>
       </c>
       <c r="K1486" t="inlineStr">
@@ -70402,12 +70378,12 @@
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>ליס טוק פודקאסט</t>
+          <t>קורסים לנשות מקצוע בתחום ההריון לידה והורות ראשונית</t>
         </is>
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>pregnancy_podcast</t>
+          <t>community_manager</t>
         </is>
       </c>
       <c r="D1487" t="inlineStr">
@@ -70417,17 +70393,17 @@
       </c>
       <c r="E1487" t="inlineStr">
         <is>
-          <t>creator</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F1487" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/lis/about/lis-talk-1-25/</t>
+          <t>https://www.israelidoula.co.il/all-courses</t>
         </is>
       </c>
       <c r="G1487" t="inlineStr">
         <is>
-          <t>rfu-refunds@tlvmc.gov.il</t>
+          <t>sivan@israelidoula.co.il</t>
         </is>
       </c>
       <c r="H1487" t="inlineStr">
@@ -70436,11 +70412,11 @@
         </is>
       </c>
       <c r="I1487" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J1487" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/unit-index-page/clinics-institutes/</t>
+          <t>https://www.israelidoula.co.il/all-courses</t>
         </is>
       </c>
       <c r="K1487" t="inlineStr">
@@ -70455,12 +70431,12 @@
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>מכללת ללדת</t>
+          <t>מעקב הריון שבועי</t>
         </is>
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>childbirth_school</t>
+          <t>women_health_creator</t>
         </is>
       </c>
       <c r="D1488" t="inlineStr">
@@ -70470,30 +70446,30 @@
       </c>
       <c r="E1488" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>creator</t>
         </is>
       </c>
       <c r="F1488" t="inlineStr">
         <is>
-          <t>https://www.study.co.il/קורס-מדריכות-הכנה-ללידה-ביהס-ללדת/</t>
+          <t>https://www.babylis.co.il/weekly-pregnancy-tracking-guide/</t>
         </is>
       </c>
       <c r="G1488" t="inlineStr">
         <is>
-          <t>office@laledetschool.co.il</t>
+          <t>info@medcalc.co.il</t>
         </is>
       </c>
       <c r="H1488" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>BUSINESS_OR_COMMUNITY</t>
         </is>
       </c>
       <c r="I1488" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J1488" t="inlineStr">
         <is>
-          <t>https://get-marketing.co.il/laledetschool/</t>
+          <t>https://medcalc.co.il/contact/</t>
         </is>
       </c>
       <c r="K1488" t="inlineStr">
@@ -70508,12 +70484,12 @@
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>קורס הכשרת מדריכות היפנובירתינג פרונטלי בתל אביב</t>
+          <t>ליס טוק פודקאסט</t>
         </is>
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>childbirth_school</t>
+          <t>pregnancy_podcast</t>
         </is>
       </c>
       <c r="D1489" t="inlineStr">
@@ -70523,30 +70499,30 @@
       </c>
       <c r="E1489" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>creator</t>
         </is>
       </c>
       <c r="F1489" t="inlineStr">
         <is>
-          <t>https://www.leidaraka.co.il/event/קורס-הכשרת-מדריכות-היפנובירתינג-פרונ/2026-11-24/</t>
+          <t>https://www.tasmc.org.il/lis/about/lis-talk-1-25/</t>
         </is>
       </c>
       <c r="G1489" t="inlineStr">
         <is>
-          <t>leidaraka@gmail.com</t>
+          <t>rfu-refunds@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="H1489" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>BUSINESS_OR_COMMUNITY</t>
         </is>
       </c>
       <c r="I1489" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J1489" t="inlineStr">
         <is>
-          <t>https://www.leidaraka.co.il/event/%D7%A7%D7%95%D7%A8%D7%A1-%D7%94%D7%9B%D7%A9%D7%A8%D7%AA-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%99%D7%A4%D7%A0%D7%95%D7%91%D7%99%D7%A8%D7%AA%D7%99%D7%A0%D7%92-%D7%A4%D7%A8%D7%95%D7%A0/2026-11-24/</t>
+          <t>https://www.tasmc.org.il/unit-index-page/clinics-institutes/</t>
         </is>
       </c>
       <c r="K1489" t="inlineStr">
@@ -70561,12 +70537,12 @@
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>לגדל</t>
+          <t>מכללת ללדת</t>
         </is>
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>community_manager</t>
+          <t>childbirth_school</t>
         </is>
       </c>
       <c r="D1490" t="inlineStr">
@@ -70576,22 +70552,22 @@
       </c>
       <c r="E1490" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>org</t>
         </is>
       </c>
       <c r="F1490" t="inlineStr">
         <is>
-          <t>https://www.guidestar.org.il/organization/580637445</t>
+          <t>https://www.study.co.il/קורס-מדריכות-הכנה-ללידה-ביהס-ללדת/</t>
         </is>
       </c>
       <c r="G1490" t="inlineStr">
         <is>
-          <t>s9763323@gmail.com</t>
+          <t>office@laledetschool.co.il</t>
         </is>
       </c>
       <c r="H1490" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="I1490" t="n">
@@ -70599,7 +70575,7 @@
       </c>
       <c r="J1490" t="inlineStr">
         <is>
-          <t>https://www.jgive.com/new/he/ils/charity-organizations/3869</t>
+          <t>https://get-marketing.co.il/laledetschool/</t>
         </is>
       </c>
       <c r="K1490" t="inlineStr">
@@ -70614,12 +70590,12 @@
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>נפש אחת בישראל</t>
+          <t>קורס הכשרת מדריכות היפנובירתינג פרונטלי בתל אביב</t>
         </is>
       </c>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>community_manager</t>
+          <t>childbirth_school</t>
         </is>
       </c>
       <c r="D1491" t="inlineStr">
@@ -70629,22 +70605,22 @@
       </c>
       <c r="E1491" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>org</t>
         </is>
       </c>
       <c r="F1491" t="inlineStr">
         <is>
-          <t>https://nefeshachat.co.il/</t>
+          <t>https://www.leidaraka.co.il/event/קורס-הכשרת-מדריכות-היפנובירתינג-פרונ/2026-11-24/</t>
         </is>
       </c>
       <c r="G1491" t="inlineStr">
         <is>
-          <t>nefesh@netvision.net.il</t>
+          <t>leidaraka@gmail.com</t>
         </is>
       </c>
       <c r="H1491" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="I1491" t="n">
@@ -70652,7 +70628,7 @@
       </c>
       <c r="J1491" t="inlineStr">
         <is>
-          <t>https://nefeshachat.co.il/contact/</t>
+          <t>https://www.leidaraka.co.il/event/%D7%A7%D7%95%D7%A8%D7%A1-%D7%94%D7%9B%D7%A9%D7%A8%D7%AA-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%99%D7%A4%D7%A0%D7%95%D7%91%D7%99%D7%A8%D7%AA%D7%99%D7%A0%D7%92-%D7%A4%D7%A8%D7%95%D7%A0/2026-11-24/</t>
         </is>
       </c>
       <c r="K1491" t="inlineStr">
@@ -70667,12 +70643,12 @@
       </c>
       <c r="B1492" t="inlineStr">
         <is>
-          <t>אודות</t>
+          <t>לגדל</t>
         </is>
       </c>
       <c r="C1492" t="inlineStr">
         <is>
-          <t>doula_school</t>
+          <t>community_manager</t>
         </is>
       </c>
       <c r="D1492" t="inlineStr">
@@ -70682,22 +70658,22 @@
       </c>
       <c r="E1492" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F1492" t="inlineStr">
         <is>
-          <t>https://www.leidaschool.co.il/untitled-c1pn</t>
+          <t>https://www.guidestar.org.il/organization/580637445</t>
         </is>
       </c>
       <c r="G1492" t="inlineStr">
         <is>
-          <t>ruti@leida.co.il</t>
+          <t>s9763323@gmail.com</t>
         </is>
       </c>
       <c r="H1492" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>BUSINESS_OR_COMMUNITY</t>
         </is>
       </c>
       <c r="I1492" t="n">
@@ -70705,7 +70681,7 @@
       </c>
       <c r="J1492" t="inlineStr">
         <is>
-          <t>https://www.leidaschool.co.il/contact</t>
+          <t>https://www.jgive.com/new/he/ils/charity-organizations/3869</t>
         </is>
       </c>
       <c r="K1492" t="inlineStr">
@@ -70720,12 +70696,12 @@
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>ד"ר דוד איסקוב מרפאת פוריות</t>
+          <t>נפש אחת בישראל</t>
         </is>
       </c>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>facebook_group_admin</t>
+          <t>community_manager</t>
         </is>
       </c>
       <c r="D1493" t="inlineStr">
@@ -70740,12 +70716,12 @@
       </c>
       <c r="F1493" t="inlineStr">
         <is>
-          <t>https://www.rofenashim.co.il/</t>
+          <t>https://nefeshachat.co.il/</t>
         </is>
       </c>
       <c r="G1493" t="inlineStr">
         <is>
-          <t>dr.dissakov@gmail.com</t>
+          <t>nefesh@netvision.net.il</t>
         </is>
       </c>
       <c r="H1493" t="inlineStr">
@@ -70758,7 +70734,7 @@
       </c>
       <c r="J1493" t="inlineStr">
         <is>
-          <t>https://www.rofenashim.co.il/maternity/</t>
+          <t>https://nefeshachat.co.il/contact/</t>
         </is>
       </c>
       <c r="K1493" t="inlineStr">
@@ -70773,12 +70749,12 @@
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>הפריה חוץ גופית(IVF)</t>
+          <t>אודות</t>
         </is>
       </c>
       <c r="C1494" t="inlineStr">
         <is>
-          <t>facebook_group_admin</t>
+          <t>doula_school</t>
         </is>
       </c>
       <c r="D1494" t="inlineStr">
@@ -70788,22 +70764,22 @@
       </c>
       <c r="E1494" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>org</t>
         </is>
       </c>
       <c r="F1494" t="inlineStr">
         <is>
-          <t>https://www.barzilaimc.org.il/</t>
+          <t>https://www.leidaschool.co.il/untitled-c1pn</t>
         </is>
       </c>
       <c r="G1494" t="inlineStr">
         <is>
-          <t>iliabord78@gmail.com</t>
+          <t>ruti@leida.co.il</t>
         </is>
       </c>
       <c r="H1494" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="I1494" t="n">
@@ -70811,7 +70787,7 @@
       </c>
       <c r="J1494" t="inlineStr">
         <is>
-          <t>https://bord-ivf.co.il/%D7%94%D7%A4%D7%A8%D7%99%D7%94-%D7%97%D7%95%D7%A5-%D7%92%D7%95%D7%A4%D7%99%D7%AA-ivf/</t>
+          <t>https://www.leidaschool.co.il/contact</t>
         </is>
       </c>
       <c r="K1494" t="inlineStr">
@@ -70826,7 +70802,7 @@
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>ליגת לה לצ'ה</t>
+          <t>ד"ר דוד איסקוב מרפאת פוריות</t>
         </is>
       </c>
       <c r="C1495" t="inlineStr">
@@ -70846,12 +70822,12 @@
       </c>
       <c r="F1495" t="inlineStr">
         <is>
-          <t>https://www.lllisrael.org.il/</t>
+          <t>https://www.rofenashim.co.il/</t>
         </is>
       </c>
       <c r="G1495" t="inlineStr">
         <is>
-          <t>ftavens@gmail.com</t>
+          <t>dr.dissakov@gmail.com</t>
         </is>
       </c>
       <c r="H1495" t="inlineStr">
@@ -70864,7 +70840,7 @@
       </c>
       <c r="J1495" t="inlineStr">
         <is>
-          <t>https://www.chesedmatch.org/%D7%99%D7%A8%D7%95%D7%A9%D7%9C%D7%99%D7%9D/chesed-categories/%D7%9C%D7%94-%D7%9C%D7%A6-%D7%94</t>
+          <t>https://www.rofenashim.co.il/maternity/</t>
         </is>
       </c>
       <c r="K1495" t="inlineStr">
@@ -70879,12 +70855,12 @@
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>ראשי</t>
+          <t>הפריה חוץ גופית(IVF)</t>
         </is>
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>instagram_creator</t>
+          <t>facebook_group_admin</t>
         </is>
       </c>
       <c r="D1496" t="inlineStr">
@@ -70894,17 +70870,17 @@
       </c>
       <c r="E1496" t="inlineStr">
         <is>
-          <t>creator</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F1496" t="inlineStr">
         <is>
-          <t>https://xn--4dberdwph2d.xn--4dbrk0ce/</t>
+          <t>https://www.barzilaimc.org.il/</t>
         </is>
       </c>
       <c r="G1496" t="inlineStr">
         <is>
-          <t>israel@fb.com</t>
+          <t>iliabord78@gmail.com</t>
         </is>
       </c>
       <c r="H1496" t="inlineStr">
@@ -70917,7 +70893,7 @@
       </c>
       <c r="J1496" t="inlineStr">
         <is>
-          <t>https://xn--4dberdwph2d.xn--4dbrk0ce/</t>
+          <t>https://bord-ivf.co.il/%D7%94%D7%A4%D7%A8%D7%99%D7%94-%D7%97%D7%95%D7%A5-%D7%92%D7%95%D7%A4%D7%99%D7%AA-ivf/</t>
         </is>
       </c>
       <c r="K1496" t="inlineStr">
@@ -70932,12 +70908,12 @@
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>מיכל רוזן</t>
+          <t>ליגת לה לצ'ה</t>
         </is>
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>pregnancy_podcast</t>
+          <t>facebook_group_admin</t>
         </is>
       </c>
       <c r="D1497" t="inlineStr">
@@ -70947,17 +70923,17 @@
       </c>
       <c r="E1497" t="inlineStr">
         <is>
-          <t>creator</t>
+          <t>community</t>
         </is>
       </c>
       <c r="F1497" t="inlineStr">
         <is>
-          <t>https://sobada.co.il/practitioner/michal_rosen</t>
+          <t>https://www.lllisrael.org.il/</t>
         </is>
       </c>
       <c r="G1497" t="inlineStr">
         <is>
-          <t>michal@curaclinic.co.il</t>
+          <t>ftavens@gmail.com</t>
         </is>
       </c>
       <c r="H1497" t="inlineStr">
@@ -70970,7 +70946,7 @@
       </c>
       <c r="J1497" t="inlineStr">
         <is>
-          <t>https://sobada.co.il/practitioner/michal_rosen</t>
+          <t>https://www.chesedmatch.org/%D7%99%D7%A8%D7%95%D7%A9%D7%9C%D7%99%D7%9D/chesed-categories/%D7%9C%D7%94-%D7%9C%D7%A6-%D7%94</t>
         </is>
       </c>
       <c r="K1497" t="inlineStr">
@@ -70985,12 +70961,12 @@
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>פודקאסט לידה רכה</t>
+          <t>ראשי</t>
         </is>
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>pregnancy_podcast</t>
+          <t>instagram_creator</t>
         </is>
       </c>
       <c r="D1498" t="inlineStr">
@@ -71005,12 +70981,12 @@
       </c>
       <c r="F1498" t="inlineStr">
         <is>
-          <t>https://www.leidaraka.co.il/thepodcast/</t>
+          <t>https://xn--4dberdwph2d.xn--4dbrk0ce/</t>
         </is>
       </c>
       <c r="G1498" t="inlineStr">
         <is>
-          <t>leidaraka@gmail.com</t>
+          <t>israel@fb.com</t>
         </is>
       </c>
       <c r="H1498" t="inlineStr">
@@ -71023,7 +70999,7 @@
       </c>
       <c r="J1498" t="inlineStr">
         <is>
-          <t>https://www.leidaraka.co.il/thepodcast/</t>
+          <t>https://xn--4dberdwph2d.xn--4dbrk0ce/</t>
         </is>
       </c>
       <c r="K1498" t="inlineStr">
@@ -71038,12 +71014,12 @@
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>Medonna- נשים בשביל הבריאות</t>
+          <t>מיכל רוזן</t>
         </is>
       </c>
       <c r="C1499" t="inlineStr">
         <is>
-          <t>women_health_creator</t>
+          <t>pregnancy_podcast</t>
         </is>
       </c>
       <c r="D1499" t="inlineStr">
@@ -71058,12 +71034,12 @@
       </c>
       <c r="F1499" t="inlineStr">
         <is>
-          <t>https://il.linkedin.com/company/medonna</t>
+          <t>https://sobada.co.il/practitioner/michal_rosen</t>
         </is>
       </c>
       <c r="G1499" t="inlineStr">
         <is>
-          <t>johndoe@company.com</t>
+          <t>michal@curaclinic.co.il</t>
         </is>
       </c>
       <c r="H1499" t="inlineStr">
@@ -71076,7 +71052,7 @@
       </c>
       <c r="J1499" t="inlineStr">
         <is>
-          <t>https://prospeo.io/c/medonna</t>
+          <t>https://sobada.co.il/practitioner/michal_rosen</t>
         </is>
       </c>
       <c r="K1499" t="inlineStr">
@@ -71091,12 +71067,12 @@
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>ביקורת ומעקב לאחר לידה</t>
+          <t>פודקאסט לידה רכה</t>
         </is>
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>women_health_creator</t>
+          <t>pregnancy_podcast</t>
         </is>
       </c>
       <c r="D1500" t="inlineStr">
@@ -71111,12 +71087,12 @@
       </c>
       <c r="F1500" t="inlineStr">
         <is>
-          <t>https://drroteminbar.co.il/postpartum-checkup/</t>
+          <t>https://www.leidaraka.co.il/thepodcast/</t>
         </is>
       </c>
       <c r="G1500" t="inlineStr">
         <is>
-          <t>drroteminbar@gmail.com</t>
+          <t>leidaraka@gmail.com</t>
         </is>
       </c>
       <c r="H1500" t="inlineStr">
@@ -71129,10 +71105,116 @@
       </c>
       <c r="J1500" t="inlineStr">
         <is>
+          <t>https://www.leidaraka.co.il/thepodcast/</t>
+        </is>
+      </c>
+      <c r="K1500" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="n">
+        <v>4</v>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>Medonna- נשים בשביל הבריאות</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>women_health_creator</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>creator</t>
+        </is>
+      </c>
+      <c r="F1501" t="inlineStr">
+        <is>
+          <t>https://il.linkedin.com/company/medonna</t>
+        </is>
+      </c>
+      <c r="G1501" t="inlineStr">
+        <is>
+          <t>johndoe@company.com</t>
+        </is>
+      </c>
+      <c r="H1501" t="inlineStr">
+        <is>
+          <t>BUSINESS_OR_COMMUNITY</t>
+        </is>
+      </c>
+      <c r="I1501" t="n">
+        <v>75</v>
+      </c>
+      <c r="J1501" t="inlineStr">
+        <is>
+          <t>https://prospeo.io/c/medonna</t>
+        </is>
+      </c>
+      <c r="K1501" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="n">
+        <v>4</v>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>ביקורת ומעקב לאחר לידה</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>women_health_creator</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>creator</t>
+        </is>
+      </c>
+      <c r="F1502" t="inlineStr">
+        <is>
           <t>https://drroteminbar.co.il/postpartum-checkup/</t>
         </is>
       </c>
-      <c r="K1500" t="inlineStr">
+      <c r="G1502" t="inlineStr">
+        <is>
+          <t>drroteminbar@gmail.com</t>
+        </is>
+      </c>
+      <c r="H1502" t="inlineStr">
+        <is>
+          <t>BUSINESS_OR_COMMUNITY</t>
+        </is>
+      </c>
+      <c r="I1502" t="n">
+        <v>75</v>
+      </c>
+      <c r="J1502" t="inlineStr">
+        <is>
+          <t>https://drroteminbar.co.il/postpartum-checkup/</t>
+        </is>
+      </c>
+      <c r="K1502" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
